--- a/tables/phenotype_associations.xlsx
+++ b/tables/phenotype_associations.xlsx
@@ -357,17 +357,17 @@
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>group</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>predictor_label</t>
+          <t>Predictor</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>display_term</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
